--- a/IntelliSource Dashboard KPI Changes a.xlsx
+++ b/IntelliSource Dashboard KPI Changes a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryan\OneDrive\Documents\GitHub\kpmg-intelliflow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD905E0-6413-4F8A-8B6A-0B3327B09207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1A24C6-B785-4B43-9727-B64F9A29AA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>Procurement Dashboard — KPIs</t>
   </si>
@@ -494,6 +494,51 @@
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -503,56 +548,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -838,7 +838,7 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="62.33203125" customWidth="1"/>
@@ -847,294 +847,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="16" t="s">
+      <c r="F6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="5">
         <v>2</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="17" t="s">
+      <c r="F7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="2">
         <v>3</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="16" t="s">
+      <c r="F8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="346.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="5">
         <v>4</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="171" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="2">
         <v>5</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="204" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="5">
         <v>6</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="15" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="286.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+      <c r="A12" s="2">
         <v>7</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="5">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="14"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="5">
         <v>9</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="15" t="s">
+      <c r="C14" s="14"/>
+      <c r="D14" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="17" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="5">
         <v>10</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="15" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="17" t="s">
+      <c r="E15" s="10"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
+      <c r="A16" s="7"/>
     </row>
     <row r="18" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
     </row>
     <row r="19" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="5">
